--- a/reports/Debug-purgatory-20260104/Month to Date (Prior Year)_Visits.xlsx
+++ b/reports/Debug-purgatory-20260104/Month to Date (Prior Year)_Visits.xlsx
@@ -31,10 +31,10 @@
     <t>Location</t>
   </si>
   <si>
-    <t>Purgatory Tickets</t>
+    <t>Purgatory Passes</t>
   </si>
   <si>
-    <t>Purgatory Passes</t>
+    <t>Purgatory Comp Tickets</t>
   </si>
   <si>
     <t>Purgatory Uplift Tickets</t>
@@ -43,7 +43,7 @@
     <t>Purgatory Coaster</t>
   </si>
   <si>
-    <t>Purgatory Comp Tickets</t>
+    <t>Purgatory Tickets</t>
   </si>
 </sst>
 </file>
@@ -437,7 +437,7 @@
         <v>45658</v>
       </c>
       <c r="C2" s="2">
-        <v>2335</v>
+        <v>2027</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>5</v>
@@ -448,13 +448,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>45659</v>
+        <v>45660</v>
       </c>
       <c r="C3" s="2">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -462,13 +462,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="2">
-        <v>45659</v>
+        <v>45661</v>
       </c>
       <c r="C4" s="2">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -476,13 +476,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="2">
-        <v>45660</v>
+        <v>45658</v>
       </c>
       <c r="C5" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -490,13 +490,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="2">
-        <v>45660</v>
+        <v>45658</v>
       </c>
       <c r="C6" s="2">
-        <v>303</v>
+        <v>2</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -504,10 +504,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="2">
-        <v>45661</v>
+        <v>45658</v>
       </c>
       <c r="C7" s="2">
-        <v>1656</v>
+        <v>147</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
@@ -518,13 +518,13 @@
         <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="C8" s="2">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -532,13 +532,13 @@
         <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>45658</v>
+        <v>45660</v>
       </c>
       <c r="C9" s="2">
-        <v>380</v>
+        <v>1733</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -546,13 +546,13 @@
         <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>45658</v>
+        <v>45661</v>
       </c>
       <c r="C10" s="2">
-        <v>684</v>
+        <v>101</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -560,13 +560,13 @@
         <v>1</v>
       </c>
       <c r="B11" s="2">
-        <v>45658</v>
+        <v>45661</v>
       </c>
       <c r="C11" s="2">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -574,13 +574,13 @@
         <v>1</v>
       </c>
       <c r="B12" s="2">
-        <v>45659</v>
+        <v>45661</v>
       </c>
       <c r="C12" s="2">
-        <v>72</v>
+        <v>130</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -588,13 +588,13 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>45660</v>
+        <v>45658</v>
       </c>
       <c r="C13" s="2">
-        <v>2</v>
+        <v>86</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -602,13 +602,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="2">
-        <v>45661</v>
+        <v>45659</v>
       </c>
       <c r="C14" s="2">
-        <v>487</v>
+        <v>2</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -616,10 +616,10 @@
         <v>1</v>
       </c>
       <c r="B15" s="2">
-        <v>45658</v>
+        <v>45660</v>
       </c>
       <c r="C15" s="2">
-        <v>4</v>
+        <v>672</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>6</v>
@@ -630,13 +630,13 @@
         <v>1</v>
       </c>
       <c r="B16" s="2">
-        <v>45658</v>
+        <v>45660</v>
       </c>
       <c r="C16" s="2">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -644,13 +644,13 @@
         <v>1</v>
       </c>
       <c r="B17" s="2">
-        <v>45658</v>
+        <v>45661</v>
       </c>
       <c r="C17" s="2">
-        <v>147</v>
+        <v>1965</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -658,13 +658,13 @@
         <v>1</v>
       </c>
       <c r="B18" s="2">
-        <v>45659</v>
+        <v>45658</v>
       </c>
       <c r="C18" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -672,10 +672,10 @@
         <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>45660</v>
+        <v>45659</v>
       </c>
       <c r="C19" s="2">
-        <v>1733</v>
+        <v>712</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>6</v>
@@ -686,13 +686,13 @@
         <v>1</v>
       </c>
       <c r="B20" s="2">
-        <v>45661</v>
+        <v>45659</v>
       </c>
       <c r="C20" s="2">
-        <v>101</v>
+        <v>1567</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -700,13 +700,13 @@
         <v>1</v>
       </c>
       <c r="B21" s="2">
-        <v>45661</v>
+        <v>45659</v>
       </c>
       <c r="C21" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -714,13 +714,13 @@
         <v>1</v>
       </c>
       <c r="B22" s="2">
-        <v>45661</v>
+        <v>45659</v>
       </c>
       <c r="C22" s="2">
-        <v>130</v>
+        <v>175</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -728,13 +728,13 @@
         <v>1</v>
       </c>
       <c r="B23" s="2">
-        <v>45658</v>
+        <v>45660</v>
       </c>
       <c r="C23" s="2">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -742,13 +742,13 @@
         <v>1</v>
       </c>
       <c r="B24" s="2">
-        <v>45659</v>
+        <v>45661</v>
       </c>
       <c r="C24" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -756,13 +756,13 @@
         <v>1</v>
       </c>
       <c r="B25" s="2">
-        <v>45660</v>
+        <v>45661</v>
       </c>
       <c r="C25" s="2">
-        <v>672</v>
+        <v>22</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -770,13 +770,13 @@
         <v>1</v>
       </c>
       <c r="B26" s="2">
-        <v>45660</v>
+        <v>45658</v>
       </c>
       <c r="C26" s="2">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -784,13 +784,13 @@
         <v>1</v>
       </c>
       <c r="B27" s="2">
-        <v>45661</v>
+        <v>45658</v>
       </c>
       <c r="C27" s="2">
-        <v>1965</v>
+        <v>380</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -801,7 +801,7 @@
         <v>45658</v>
       </c>
       <c r="C28" s="2">
-        <v>2027</v>
+        <v>684</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>6</v>
@@ -812,13 +812,13 @@
         <v>1</v>
       </c>
       <c r="B29" s="2">
-        <v>45660</v>
+        <v>45658</v>
       </c>
       <c r="C29" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -826,13 +826,13 @@
         <v>1</v>
       </c>
       <c r="B30" s="2">
-        <v>45661</v>
+        <v>45659</v>
       </c>
       <c r="C30" s="2">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -840,13 +840,13 @@
         <v>1</v>
       </c>
       <c r="B31" s="2">
-        <v>45658</v>
+        <v>45660</v>
       </c>
       <c r="C31" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -854,10 +854,10 @@
         <v>1</v>
       </c>
       <c r="B32" s="2">
-        <v>45659</v>
+        <v>45661</v>
       </c>
       <c r="C32" s="2">
-        <v>26</v>
+        <v>487</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>6</v>
@@ -868,13 +868,13 @@
         <v>1</v>
       </c>
       <c r="B33" s="2">
-        <v>45660</v>
+        <v>45658</v>
       </c>
       <c r="C33" s="2">
         <v>1</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -882,13 +882,13 @@
         <v>1</v>
       </c>
       <c r="B34" s="2">
-        <v>45660</v>
+        <v>45659</v>
       </c>
       <c r="C34" s="2">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -899,10 +899,10 @@
         <v>45660</v>
       </c>
       <c r="C35" s="2">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -913,7 +913,7 @@
         <v>45660</v>
       </c>
       <c r="C36" s="2">
-        <v>1871</v>
+        <v>1</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>5</v>
@@ -927,10 +927,10 @@
         <v>45660</v>
       </c>
       <c r="C37" s="2">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -941,10 +941,10 @@
         <v>45660</v>
       </c>
       <c r="C38" s="2">
-        <v>26</v>
+        <v>1871</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -955,10 +955,10 @@
         <v>45660</v>
       </c>
       <c r="C39" s="2">
-        <v>179</v>
+        <v>2</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -966,13 +966,13 @@
         <v>1</v>
       </c>
       <c r="B40" s="2">
-        <v>45661</v>
+        <v>45660</v>
       </c>
       <c r="C40" s="2">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -980,13 +980,13 @@
         <v>1</v>
       </c>
       <c r="B41" s="2">
-        <v>45658</v>
+        <v>45660</v>
       </c>
       <c r="C41" s="2">
-        <v>22</v>
+        <v>179</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -994,13 +994,13 @@
         <v>1</v>
       </c>
       <c r="B42" s="2">
-        <v>45658</v>
+        <v>45661</v>
       </c>
       <c r="C42" s="2">
+        <v>6</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1008,13 +1008,13 @@
         <v>1</v>
       </c>
       <c r="B43" s="2">
-        <v>45659</v>
+        <v>45658</v>
       </c>
       <c r="C43" s="2">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1022,13 +1022,13 @@
         <v>1</v>
       </c>
       <c r="B44" s="2">
-        <v>45659</v>
+        <v>45658</v>
       </c>
       <c r="C44" s="2">
-        <v>311</v>
+        <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1039,7 +1039,7 @@
         <v>45659</v>
       </c>
       <c r="C45" s="2">
-        <v>2084</v>
+        <v>5</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>5</v>
@@ -1050,13 +1050,13 @@
         <v>1</v>
       </c>
       <c r="B46" s="2">
-        <v>45661</v>
+        <v>45659</v>
       </c>
       <c r="C46" s="2">
-        <v>25</v>
+        <v>311</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1064,13 +1064,13 @@
         <v>1</v>
       </c>
       <c r="B47" s="2">
-        <v>45661</v>
+        <v>45659</v>
       </c>
       <c r="C47" s="2">
-        <v>1</v>
+        <v>2084</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1078,13 +1078,13 @@
         <v>1</v>
       </c>
       <c r="B48" s="2">
-        <v>45658</v>
+        <v>45661</v>
       </c>
       <c r="C48" s="2">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1092,13 +1092,13 @@
         <v>1</v>
       </c>
       <c r="B49" s="2">
-        <v>45659</v>
+        <v>45661</v>
       </c>
       <c r="C49" s="2">
-        <v>712</v>
+        <v>1</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1106,13 +1106,13 @@
         <v>1</v>
       </c>
       <c r="B50" s="2">
-        <v>45659</v>
+        <v>45658</v>
       </c>
       <c r="C50" s="2">
-        <v>1567</v>
+        <v>2335</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1123,10 +1123,10 @@
         <v>45659</v>
       </c>
       <c r="C51" s="2">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1137,10 +1137,10 @@
         <v>45659</v>
       </c>
       <c r="C52" s="2">
-        <v>175</v>
+        <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1151,10 +1151,10 @@
         <v>45660</v>
       </c>
       <c r="C53" s="2">
-        <v>99</v>
+        <v>5</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1162,13 +1162,13 @@
         <v>1</v>
       </c>
       <c r="B54" s="2">
-        <v>45661</v>
+        <v>45660</v>
       </c>
       <c r="C54" s="2">
-        <v>1</v>
+        <v>303</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1179,10 +1179,10 @@
         <v>45661</v>
       </c>
       <c r="C55" s="2">
-        <v>22</v>
+        <v>1656</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
